--- a/output/2026-09-13_16_Croazia_Bjelovarsko-bilogorska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-13_16_Croazia_Bjelovarsko-bilogorska_ATEX_Equipment-Services.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Distribuzione/vendita ingrosso attrezzature Ex, rappresentante STAHL. Nessun sito ufficiale proprio individuato, email non reperita. Fuori dalla contea Bjelovarsko-bilogorska richiesta (nessun candidato trovato in loco).</t>
+          <t>Distribuzione/vendita ingrosso attrezzature Ex, rappresentante STAHL. Nessun sito ufficiale proprio individuato, email non reperita. Fuori dalla contea Bjelovarsko-bilogorska richiesta (nessun candidato trovato in loco). [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ente Notificato UE n. 2829 e Certification Body IECEx per apparecchiature/sistemi ATEX. NON è un distributore ma organismo di certificazione: partner istituzionale rilevante, non canale di vendita.</t>
+          <t>Ente Notificato UE n. 2829 e Certification Body IECEx per apparecchiature/sistemi ATEX. NON è un distributore ma organismo di certificazione: partner istituzionale rilevante, non canale di vendita. [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Distributore ufficiale Nilfisk: aspiratori industriali con modelli ATEX confermati (CFM 3907/18 Z21 ATEX, CFM VHS110 Z22 EXA ATEX), catalogo online verificato.</t>
+          <t>Distributore ufficiale Nilfisk: aspiratori industriali con modelli ATEX confermati (CFM 3907/18 Z21 ATEX, CFM VHS110 Z22 EXA ATEX), catalogo online verificato. [DUPLICATO — vedi anche: 2026-09-07_19_Croazia_Zagrebacka_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">

--- a/output/2026-09-13_16_Croazia_Bjelovarsko-bilogorska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-13_16_Croazia_Bjelovarsko-bilogorska_ATEX_Equipment-Services.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
